--- a/144/DQ Templates and Instructions/Topic 4 DQ 2/Topic 4 DQ 2.xlsx
+++ b/144/DQ Templates and Instructions/Topic 4 DQ 2/Topic 4 DQ 2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 4 DQ 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="617" documentId="8_{C5F6D942-BE47-4B16-B7DF-0F8A5C8F158C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24A9FB7D-AA64-4DA8-B9B8-CB4B425DBC97}"/>
+  <xr:revisionPtr revIDLastSave="619" documentId="8_{C5F6D942-BE47-4B16-B7DF-0F8A5C8F158C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48115DAD-E626-4849-BE22-EFDC14339F63}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4FCF7FA6-22BB-4545-AB27-D5B8AACA448D}"/>
+    <workbookView xWindow="3540" yWindow="345" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{4FCF7FA6-22BB-4545-AB27-D5B8AACA448D}"/>
   </bookViews>
   <sheets>
     <sheet name="Goals and Instructions" sheetId="5" r:id="rId1"/>
@@ -1098,7 +1098,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1221,18 +1221,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1324,6 +1312,118 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -1352,337 +1452,233 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1716,13 +1712,6 @@
         <i val="0"/>
         <color rgb="FF00B050"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.59996337778862885"/>
@@ -1735,6 +1724,13 @@
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2579,9 +2575,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2619,7 +2615,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2725,7 +2721,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2867,7 +2863,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2886,53 +2882,53 @@
       <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="61"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="58"/>
     </row>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="62"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="64"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="61"/>
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="62"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="64"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="61"/>
     </row>
     <row r="5" spans="2:9">
       <c r="B5" s="12"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="64"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="61"/>
     </row>
     <row r="6" spans="2:9" ht="15.75" thickBot="1">
-      <c r="D6" s="65"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="67"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="64"/>
     </row>
     <row r="7" spans="2:9" ht="15.75" thickBot="1"/>
     <row r="8" spans="2:9" ht="19.5" thickBot="1">
@@ -2986,10 +2982,10 @@
       <c r="C2" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="98" t="s">
+      <c r="D2" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="99"/>
+      <c r="E2" s="66"/>
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
     </row>
@@ -3010,18 +3006,18 @@
       <c r="I4" s="16"/>
     </row>
     <row r="5" spans="2:10" ht="16.5" thickTop="1">
-      <c r="B5" s="104" t="s">
+      <c r="B5" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="105"/>
+      <c r="C5" s="72"/>
       <c r="D5" s="16"/>
       <c r="E5" s="19">
         <v>15</v>
       </c>
-      <c r="F5" s="118" t="s">
+      <c r="F5" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="G5" s="119"/>
+      <c r="G5" s="86"/>
       <c r="H5" s="20"/>
       <c r="I5" s="20"/>
     </row>
@@ -3036,10 +3032,10 @@
       <c r="E6" s="21">
         <v>15</v>
       </c>
-      <c r="F6" s="120" t="s">
+      <c r="F6" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="G6" s="121"/>
+      <c r="G6" s="88"/>
       <c r="H6" s="22"/>
       <c r="I6" s="22"/>
     </row>
@@ -3054,10 +3050,10 @@
       <c r="E7" s="23">
         <v>16</v>
       </c>
-      <c r="F7" s="122" t="s">
+      <c r="F7" s="89" t="s">
         <v>95</v>
       </c>
-      <c r="G7" s="123"/>
+      <c r="G7" s="90"/>
       <c r="H7" s="20"/>
       <c r="I7" s="20"/>
     </row>
@@ -3072,10 +3068,10 @@
       <c r="E8" s="24">
         <v>16</v>
       </c>
-      <c r="F8" s="124" t="s">
+      <c r="F8" s="91" t="s">
         <v>96</v>
       </c>
-      <c r="G8" s="125"/>
+      <c r="G8" s="92"/>
       <c r="H8" s="22"/>
       <c r="I8" s="22"/>
     </row>
@@ -3088,11 +3084,11 @@
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="71" t="s">
+      <c r="F9" s="96" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="71"/>
-      <c r="H9" s="71"/>
+      <c r="G9" s="96"/>
+      <c r="H9" s="96"/>
       <c r="I9" s="16"/>
     </row>
     <row r="10" spans="2:10" ht="16.5" thickBot="1">
@@ -3109,37 +3105,37 @@
     </row>
     <row r="11" spans="2:10" ht="16.5" thickTop="1" thickBot="1"/>
     <row r="12" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B12" s="106" t="s">
+      <c r="B12" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="107"/>
-      <c r="D12" s="107"/>
-      <c r="E12" s="107"/>
-      <c r="F12" s="108"/>
+      <c r="C12" s="74"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="75"/>
     </row>
     <row r="13" spans="2:10" ht="15.75" thickBot="1">
-      <c r="B13" s="109"/>
-      <c r="C13" s="110"/>
-      <c r="D13" s="110"/>
-      <c r="E13" s="110"/>
-      <c r="F13" s="111"/>
+      <c r="B13" s="76"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="78"/>
       <c r="J13" s="26"/>
     </row>
     <row r="14" spans="2:10" ht="16.899999999999999" customHeight="1">
-      <c r="B14" s="112" t="s">
+      <c r="B14" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="113"/>
-      <c r="D14" s="113"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="114"/>
+      <c r="C14" s="80"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="80"/>
+      <c r="F14" s="81"/>
     </row>
     <row r="15" spans="2:10" ht="16.899999999999999" customHeight="1" thickBot="1">
-      <c r="B15" s="115"/>
-      <c r="C15" s="116"/>
-      <c r="D15" s="116"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="117"/>
+      <c r="B15" s="82"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="84"/>
     </row>
     <row r="16" spans="2:10">
       <c r="B16" s="27" t="s">
@@ -3154,37 +3150,37 @@
       <c r="E16" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="F16" s="102" t="s">
+      <c r="F16" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="102" t="s">
+      <c r="G16" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="H16" s="100" t="s">
+      <c r="H16" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="86"/>
+      <c r="I16" s="109"/>
     </row>
     <row r="17" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B17" s="34"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="103"/>
-      <c r="G17" s="103"/>
-      <c r="H17" s="101"/>
-      <c r="I17" s="86"/>
+      <c r="B17" s="159"/>
+      <c r="C17" s="160"/>
+      <c r="D17" s="160"/>
+      <c r="E17" s="160"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="109"/>
     </row>
     <row r="18" spans="2:11" ht="14.45" customHeight="1">
-      <c r="B18" s="77" t="str">
+      <c r="B18" s="100" t="str">
         <f ca="1">IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the monthly payments to pay back a loan of $"&amp;Random!H19&amp;" in "&amp;Random!H20&amp;" years an APR of "&amp;Random!H21&amp;"% compounded monthly. Find the total amount payed on the loan and the interest payed.")</f>
         <v>Compute the monthly payments to pay back a loan of $2200 in 5 years an APR of 20.29% compounded monthly. Find the total amount payed on the loan and the interest payed.</v>
       </c>
-      <c r="C18" s="78"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="91" t="s">
+      <c r="C18" s="101"/>
+      <c r="D18" s="101"/>
+      <c r="E18" s="102"/>
+      <c r="F18" s="97"/>
+      <c r="G18" s="110" t="s">
         <v>97</v>
       </c>
       <c r="H18" s="29" t="s">
@@ -3199,49 +3195,59 @@
       <c r="K18" s="26"/>
     </row>
     <row r="19" spans="2:11">
-      <c r="B19" s="80"/>
-      <c r="C19" s="81"/>
-      <c r="D19" s="81"/>
-      <c r="E19" s="82"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="92"/>
-      <c r="H19" s="87"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="75"/>
+      <c r="B19" s="103"/>
+      <c r="C19" s="104"/>
+      <c r="D19" s="104"/>
+      <c r="E19" s="105"/>
+      <c r="F19" s="98"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="161"/>
+      <c r="I19" s="162"/>
+      <c r="J19" s="163"/>
       <c r="K19" s="26"/>
     </row>
     <row r="20" spans="2:11" ht="24" customHeight="1" thickBot="1">
-      <c r="B20" s="83"/>
-      <c r="C20" s="84"/>
-      <c r="D20" s="84"/>
-      <c r="E20" s="85"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="93"/>
-      <c r="H20" s="88"/>
-      <c r="I20" s="90"/>
-      <c r="J20" s="76"/>
+      <c r="B20" s="106"/>
+      <c r="C20" s="107"/>
+      <c r="D20" s="107"/>
+      <c r="E20" s="108"/>
+      <c r="F20" s="99"/>
+      <c r="G20" s="112"/>
+      <c r="H20" s="164"/>
+      <c r="I20" s="165"/>
+      <c r="J20" s="166"/>
       <c r="K20" s="26"/>
     </row>
     <row r="21" spans="2:11" ht="15.75" thickBot="1">
       <c r="B21" s="32"/>
-      <c r="F21" s="94" t="s">
+      <c r="F21" s="113" t="s">
         <v>92</v>
       </c>
-      <c r="G21" s="95"/>
-      <c r="H21" s="68" t="s">
+      <c r="G21" s="114"/>
+      <c r="H21" s="93" t="s">
         <v>31</v>
       </c>
-      <c r="I21" s="69"/>
-      <c r="J21" s="70"/>
+      <c r="I21" s="94"/>
+      <c r="J21" s="95"/>
       <c r="K21" s="26"/>
     </row>
     <row r="22" spans="2:11" ht="15.75" thickBot="1">
-      <c r="F22" s="96"/>
-      <c r="G22" s="97"/>
+      <c r="F22" s="115"/>
+      <c r="G22" s="116"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="04EZ75vEYzLuSc635yspVl1Pqdtqngx1OL36DW2Rvm2Pv8R8UFoFl8551fCW7aF82cNDLiYmkbGSxpHOls1U0w==" saltValue="Rqqa4jYiaDvVwlJBzKlTNQ==" spinCount="100000" sheet="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="21">
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="B18:E20"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="F21:G22"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="H16:H17"/>
     <mergeCell ref="F16:F17"/>
@@ -3253,19 +3259,9 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="B18:E20"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="F21:G22"/>
   </mergeCells>
   <conditionalFormatting sqref="H19:J19 I20:J20">
-    <cfRule type="expression" dxfId="4" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
       <formula>NOT(OR(_xlfn.ISFORMULA(H19),ISBLANK(H19)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3275,6 +3271,19 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{9DEF9615-F6B4-489E-B9ED-7F496E3768AC}">
+            <xm:f>B17=Solutions!B17</xm:f>
+            <x14:dxf>
+              <font>
+                <b/>
+                <i val="0"/>
+                <color rgb="FF00B050"/>
+              </font>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B17:E17</xm:sqref>
+        </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="expression" priority="5" id="{CABF01FD-4735-4029-8110-F24E8271B6C8}">
             <xm:f>AND(NOT(ISBLANK(H19)),ABS(H19-Solutions!H24)&lt;0.01)</xm:f>
@@ -3292,19 +3301,6 @@
             </x14:dxf>
           </x14:cfRule>
           <xm:sqref>H19:J19 I20:J20</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="1" id="{9DEF9615-F6B4-489E-B9ED-7F496E3768AC}">
-            <xm:f>B17=Solutions!B17</xm:f>
-            <x14:dxf>
-              <font>
-                <b/>
-                <i val="0"/>
-                <color rgb="FF00B050"/>
-              </font>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B17:E17</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -5318,343 +5314,351 @@
   <dimension ref="B2:J27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" style="37" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.42578125" style="46" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" style="37" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="37" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.140625" style="40" customWidth="1"/>
-    <col min="9" max="9" width="22.28515625" style="41" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.28515625" style="37" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="37"/>
+    <col min="1" max="1" width="3.7109375" style="34" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" style="43" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" style="43" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.42578125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" style="34" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="34" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.140625" style="37" customWidth="1"/>
+    <col min="9" max="9" width="22.28515625" style="38" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.28515625" style="34" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="34"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
     </row>
     <row r="3" spans="2:9">
-      <c r="B3" s="40"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
     </row>
     <row r="4" spans="2:9" ht="15.75" thickBot="1">
-      <c r="B4" s="40"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
     </row>
     <row r="5" spans="2:9" ht="16.5" thickTop="1">
-      <c r="B5" s="133" t="s">
+      <c r="B5" s="130" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="134"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
+      <c r="C5" s="131"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
     </row>
     <row r="6" spans="2:9" ht="15.75">
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
     </row>
     <row r="7" spans="2:9" ht="15.75">
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
     </row>
     <row r="8" spans="2:9" ht="15.75">
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
     </row>
     <row r="9" spans="2:9" ht="15.75">
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
     </row>
     <row r="10" spans="2:9" ht="16.5" thickBot="1">
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
     </row>
     <row r="11" spans="2:9" ht="16.5" thickTop="1" thickBot="1"/>
     <row r="12" spans="2:9">
-      <c r="B12" s="135" t="s">
+      <c r="B12" s="132" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="136"/>
-      <c r="D12" s="136"/>
-      <c r="E12" s="136"/>
-      <c r="F12" s="137"/>
+      <c r="C12" s="133"/>
+      <c r="D12" s="133"/>
+      <c r="E12" s="133"/>
+      <c r="F12" s="134"/>
     </row>
     <row r="13" spans="2:9" ht="15.75" thickBot="1">
-      <c r="B13" s="138"/>
-      <c r="C13" s="139"/>
-      <c r="D13" s="139"/>
-      <c r="E13" s="139"/>
-      <c r="F13" s="140"/>
+      <c r="B13" s="135"/>
+      <c r="C13" s="136"/>
+      <c r="D13" s="136"/>
+      <c r="E13" s="136"/>
+      <c r="F13" s="137"/>
     </row>
     <row r="14" spans="2:9" ht="16.899999999999999" customHeight="1">
-      <c r="B14" s="141" t="s">
+      <c r="B14" s="138" t="s">
         <v>78</v>
       </c>
-      <c r="C14" s="142"/>
-      <c r="D14" s="142"/>
-      <c r="E14" s="142"/>
-      <c r="F14" s="143"/>
+      <c r="C14" s="139"/>
+      <c r="D14" s="139"/>
+      <c r="E14" s="139"/>
+      <c r="F14" s="140"/>
     </row>
     <row r="15" spans="2:9" ht="16.899999999999999" customHeight="1" thickBot="1">
-      <c r="B15" s="144"/>
-      <c r="C15" s="145"/>
-      <c r="D15" s="145"/>
-      <c r="E15" s="145"/>
-      <c r="F15" s="146"/>
+      <c r="B15" s="141"/>
+      <c r="C15" s="142"/>
+      <c r="D15" s="142"/>
+      <c r="E15" s="142"/>
+      <c r="F15" s="143"/>
     </row>
     <row r="16" spans="2:9">
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="48" t="s">
+      <c r="C16" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="D16" s="48" t="s">
+      <c r="D16" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="48" t="s">
+      <c r="E16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="F16" s="147" t="s">
+      <c r="F16" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="147" t="s">
+      <c r="G16" s="144" t="s">
         <v>27</v>
       </c>
-      <c r="H16" s="155" t="s">
+      <c r="H16" s="124" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="157"/>
+      <c r="I16" s="126"/>
     </row>
     <row r="17" spans="2:10">
-      <c r="B17" s="49">
+      <c r="B17" s="46">
         <f ca="1">Random!H19</f>
         <v>2200</v>
       </c>
-      <c r="C17" s="50">
+      <c r="C17" s="47">
         <f ca="1">Random!H21%</f>
         <v>0.2029</v>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="48">
         <v>12</v>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="48">
         <f ca="1">Random!H20</f>
         <v>5</v>
       </c>
-      <c r="F17" s="148"/>
-      <c r="G17" s="148"/>
-      <c r="H17" s="156"/>
-      <c r="I17" s="157"/>
+      <c r="F17" s="145"/>
+      <c r="G17" s="145"/>
+      <c r="H17" s="125"/>
+      <c r="I17" s="126"/>
     </row>
     <row r="18" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B18" s="149" t="s">
+      <c r="B18" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="150"/>
-      <c r="D18" s="150"/>
-      <c r="E18" s="151"/>
-      <c r="F18" s="127"/>
-      <c r="G18" s="126" t="s">
+      <c r="C18" s="118"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="119"/>
+      <c r="F18" s="123"/>
+      <c r="G18" s="146" t="s">
         <v>82</v>
       </c>
-      <c r="H18" s="52" t="s">
+      <c r="H18" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="I18" s="53" t="s">
+      <c r="I18" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="J18" s="54"/>
+      <c r="J18" s="51"/>
     </row>
     <row r="19" spans="2:10">
-      <c r="B19" s="149"/>
-      <c r="C19" s="150"/>
-      <c r="D19" s="150"/>
-      <c r="E19" s="151"/>
-      <c r="F19" s="127"/>
-      <c r="G19" s="126"/>
-      <c r="H19" s="55" t="e">
+      <c r="B19" s="117"/>
+      <c r="C19" s="118"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="123"/>
+      <c r="G19" s="146"/>
+      <c r="H19" s="52" t="e">
         <f>Loans!B17*(1+Loans!C17/Loans!D17)^(Loans!D17*Loans!E17)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I19" s="56" t="e">
+      <c r="I19" s="53" t="e">
         <f>H19-Loans!B17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J19" s="54"/>
+      <c r="J19" s="51"/>
     </row>
     <row r="20" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B20" s="149"/>
-      <c r="C20" s="150"/>
-      <c r="D20" s="150"/>
-      <c r="E20" s="151"/>
-      <c r="F20" s="127"/>
-      <c r="G20" s="126" t="s">
+      <c r="B20" s="117"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="119"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="146" t="s">
         <v>85</v>
       </c>
-      <c r="H20" s="57" t="s">
+      <c r="H20" s="54" t="s">
         <v>83</v>
       </c>
-      <c r="I20" s="53" t="s">
+      <c r="I20" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="J20" s="53" t="s">
+      <c r="J20" s="50" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="21" spans="2:10">
-      <c r="B21" s="149"/>
-      <c r="C21" s="150"/>
-      <c r="D21" s="150"/>
-      <c r="E21" s="151"/>
-      <c r="F21" s="127"/>
-      <c r="G21" s="126"/>
-      <c r="H21" s="158" t="e">
+      <c r="B21" s="117"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="119"/>
+      <c r="F21" s="123"/>
+      <c r="G21" s="146"/>
+      <c r="H21" s="127" t="e">
         <f>Loans!B17*((1+Loans!C17/Loans!D17)^(Loans!D17*Loans!E17)-1)/(Loans!C17/Loans!D17)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I21" s="130">
+      <c r="I21" s="128">
         <f>Loans!B17*Loans!D17*Loans!E17</f>
         <v>0</v>
       </c>
-      <c r="J21" s="130" t="e">
+      <c r="J21" s="128" t="e">
         <f>H21-I21</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="22" spans="2:10">
-      <c r="B22" s="149"/>
-      <c r="C22" s="150"/>
-      <c r="D22" s="150"/>
-      <c r="E22" s="151"/>
-      <c r="F22" s="127"/>
-      <c r="G22" s="126"/>
-      <c r="H22" s="158"/>
-      <c r="I22" s="131"/>
-      <c r="J22" s="131"/>
+      <c r="B22" s="117"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="119"/>
+      <c r="F22" s="123"/>
+      <c r="G22" s="146"/>
+      <c r="H22" s="127"/>
+      <c r="I22" s="129"/>
+      <c r="J22" s="129"/>
     </row>
     <row r="23" spans="2:10">
-      <c r="B23" s="149"/>
-      <c r="C23" s="150"/>
-      <c r="D23" s="150"/>
-      <c r="E23" s="151"/>
-      <c r="F23" s="127"/>
-      <c r="G23" s="126" t="s">
+      <c r="B23" s="117"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="119"/>
+      <c r="F23" s="123"/>
+      <c r="G23" s="146" t="s">
         <v>87</v>
       </c>
-      <c r="H23" s="52" t="s">
+      <c r="H23" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="I23" s="53" t="s">
+      <c r="I23" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="J23" s="53" t="s">
+      <c r="J23" s="50" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="24" spans="2:10">
-      <c r="B24" s="149"/>
-      <c r="C24" s="150"/>
-      <c r="D24" s="150"/>
-      <c r="E24" s="151"/>
-      <c r="F24" s="127"/>
-      <c r="G24" s="126"/>
-      <c r="H24" s="158" t="e">
+      <c r="B24" s="117"/>
+      <c r="C24" s="118"/>
+      <c r="D24" s="118"/>
+      <c r="E24" s="119"/>
+      <c r="F24" s="123"/>
+      <c r="G24" s="146"/>
+      <c r="H24" s="127" t="e">
         <f>Loans!B17*(Loans!C17/Loans!D17)/(1-(1+Loans!C17/Loans!D17)^(-Loans!D17*Loans!E17))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I24" s="130">
+      <c r="I24" s="128">
         <f>Loans!D17*Loans!E17*Loans!H19</f>
         <v>0</v>
       </c>
-      <c r="J24" s="129">
+      <c r="J24" s="148">
         <f>I24-Loans!B17</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:10" ht="17.45" customHeight="1" thickBot="1">
-      <c r="B25" s="152"/>
-      <c r="C25" s="153"/>
-      <c r="D25" s="153"/>
-      <c r="E25" s="154"/>
-      <c r="F25" s="128"/>
-      <c r="G25" s="132"/>
-      <c r="H25" s="158"/>
-      <c r="I25" s="131"/>
-      <c r="J25" s="129"/>
+      <c r="B25" s="120"/>
+      <c r="C25" s="121"/>
+      <c r="D25" s="121"/>
+      <c r="E25" s="122"/>
+      <c r="F25" s="147"/>
+      <c r="G25" s="149"/>
+      <c r="H25" s="127"/>
+      <c r="I25" s="129"/>
+      <c r="J25" s="148"/>
     </row>
     <row r="26" spans="2:10">
-      <c r="B26" s="58"/>
-      <c r="I26" s="37"/>
+      <c r="B26" s="55"/>
+      <c r="I26" s="34"/>
     </row>
     <row r="27" spans="2:10">
-      <c r="B27" s="41"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="H27" s="37"/>
-      <c r="I27" s="37"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="34"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="K6FLfj/2GW8ZCTHv8p2xOh6RoXSFAt/EbNff2TRYiVEiR5k81I441LUk2VqjGrBYfbxIzcyIabf7eIRPuVbGfw==" saltValue="gn8DjQ/CYqWIJUrkECcB7A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="20">
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B12:F13"/>
+    <mergeCell ref="B14:F15"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
     <mergeCell ref="B18:E25"/>
     <mergeCell ref="F18:F19"/>
     <mergeCell ref="H16:H17"/>
@@ -5663,27 +5667,19 @@
     <mergeCell ref="I21:I22"/>
     <mergeCell ref="H24:H25"/>
     <mergeCell ref="I24:I25"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B12:F13"/>
-    <mergeCell ref="B14:F15"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
     <mergeCell ref="G18:G19"/>
     <mergeCell ref="F20:F22"/>
     <mergeCell ref="G20:G22"/>
     <mergeCell ref="F23:F25"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="G23:G25"/>
   </mergeCells>
-  <conditionalFormatting sqref="H24">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>AND(ABS(H24-#REF!)&lt;0.001,NOT(ISBLANK(H24)))</formula>
+  <conditionalFormatting sqref="H18:H21">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>AND(ABS(H18-#REF!)&lt;0.001,NOT(ISBLANK(H18)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H18:H21 H23">
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>AND(ABS(H18-#REF!)&lt;0.001,NOT(ISBLANK(H18)))</formula>
+  <conditionalFormatting sqref="H23:H24">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>AND(ABS(H23-#REF!)&lt;0.001,NOT(ISBLANK(H23)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5701,34 +5697,34 @@
   <sheetData>
     <row r="1" spans="2:6" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:6">
-      <c r="B2" s="159" t="s">
+      <c r="B2" s="150" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="161"/>
+      <c r="C2" s="151"/>
+      <c r="D2" s="151"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="152"/>
     </row>
     <row r="3" spans="2:6">
-      <c r="B3" s="162"/>
-      <c r="C3" s="163"/>
-      <c r="D3" s="163"/>
-      <c r="E3" s="163"/>
-      <c r="F3" s="164"/>
+      <c r="B3" s="153"/>
+      <c r="C3" s="154"/>
+      <c r="D3" s="154"/>
+      <c r="E3" s="154"/>
+      <c r="F3" s="155"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="162"/>
-      <c r="C4" s="163"/>
-      <c r="D4" s="163"/>
-      <c r="E4" s="163"/>
-      <c r="F4" s="164"/>
+      <c r="B4" s="153"/>
+      <c r="C4" s="154"/>
+      <c r="D4" s="154"/>
+      <c r="E4" s="154"/>
+      <c r="F4" s="155"/>
     </row>
     <row r="5" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B5" s="165"/>
-      <c r="C5" s="166"/>
-      <c r="D5" s="166"/>
-      <c r="E5" s="166"/>
-      <c r="F5" s="167"/>
+      <c r="B5" s="156"/>
+      <c r="C5" s="157"/>
+      <c r="D5" s="157"/>
+      <c r="E5" s="157"/>
+      <c r="F5" s="158"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5739,8 +5735,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4b388b19620a428294a52af29a503226">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f4390916c591314b5f0446846c34d485" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="674b7a4e239a9748c7aaa97e309327a4">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="600253478e594d1349e02792803dc53a" ns2:_="" ns3:_="">
     <xsd:import namespace="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
     <xsd:import namespace="18557d39-01b8-4d71-9479-3fad465290ae"/>
     <xsd:element name="properties">
@@ -5955,15 +5960,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5975,30 +5971,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5F2A7EE-DF0A-424E-863E-0C5B8EAF6BC3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC22AC1B-1134-480D-984D-E3FB18425132}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
-    <ds:schemaRef ds:uri="18557d39-01b8-4d71-9479-3fad465290ae"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC22AC1B-1134-480D-984D-E3FB18425132}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8D40D51-EB3D-4F2E-911E-703AF067E6CE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/144/DQ Templates and Instructions/Topic 4 DQ 2/Topic 4 DQ 2.xlsx
+++ b/144/DQ Templates and Instructions/Topic 4 DQ 2/Topic 4 DQ 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 4 DQ 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="619" documentId="8_{C5F6D942-BE47-4B16-B7DF-0F8A5C8F158C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48115DAD-E626-4849-BE22-EFDC14339F63}"/>
+  <xr:revisionPtr revIDLastSave="620" documentId="8_{C5F6D942-BE47-4B16-B7DF-0F8A5C8F158C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BBECDCF-CCC7-4EFB-BFBF-58ED0EFFAB18}"/>
   <bookViews>
-    <workbookView xWindow="3540" yWindow="345" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{4FCF7FA6-22BB-4545-AB27-D5B8AACA448D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4FCF7FA6-22BB-4545-AB27-D5B8AACA448D}"/>
   </bookViews>
   <sheets>
     <sheet name="Goals and Instructions" sheetId="5" r:id="rId1"/>
@@ -1285,369 +1285,6 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1656,29 +1293,392 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2882,53 +2882,53 @@
       <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="D2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="58"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="60"/>
     </row>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="59"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="63"/>
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="59"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="63"/>
     </row>
     <row r="5" spans="2:9">
       <c r="B5" s="12"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="63"/>
     </row>
     <row r="6" spans="2:9" ht="15.75" thickBot="1">
-      <c r="D6" s="62"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="63"/>
-      <c r="I6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="66"/>
     </row>
     <row r="7" spans="2:9" ht="15.75" thickBot="1"/>
     <row r="8" spans="2:9" ht="19.5" thickBot="1">
@@ -2982,10 +2982,10 @@
       <c r="C2" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="65" t="s">
+      <c r="D2" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="66"/>
+      <c r="E2" s="98"/>
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
     </row>
@@ -3006,18 +3006,18 @@
       <c r="I4" s="16"/>
     </row>
     <row r="5" spans="2:10" ht="16.5" thickTop="1">
-      <c r="B5" s="71" t="s">
+      <c r="B5" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="72"/>
+      <c r="C5" s="104"/>
       <c r="D5" s="16"/>
       <c r="E5" s="19">
         <v>15</v>
       </c>
-      <c r="F5" s="85" t="s">
+      <c r="F5" s="117" t="s">
         <v>93</v>
       </c>
-      <c r="G5" s="86"/>
+      <c r="G5" s="118"/>
       <c r="H5" s="20"/>
       <c r="I5" s="20"/>
     </row>
@@ -3032,10 +3032,10 @@
       <c r="E6" s="21">
         <v>15</v>
       </c>
-      <c r="F6" s="87" t="s">
+      <c r="F6" s="119" t="s">
         <v>94</v>
       </c>
-      <c r="G6" s="88"/>
+      <c r="G6" s="120"/>
       <c r="H6" s="22"/>
       <c r="I6" s="22"/>
     </row>
@@ -3050,10 +3050,10 @@
       <c r="E7" s="23">
         <v>16</v>
       </c>
-      <c r="F7" s="89" t="s">
+      <c r="F7" s="121" t="s">
         <v>95</v>
       </c>
-      <c r="G7" s="90"/>
+      <c r="G7" s="122"/>
       <c r="H7" s="20"/>
       <c r="I7" s="20"/>
     </row>
@@ -3068,10 +3068,10 @@
       <c r="E8" s="24">
         <v>16</v>
       </c>
-      <c r="F8" s="91" t="s">
+      <c r="F8" s="123" t="s">
         <v>96</v>
       </c>
-      <c r="G8" s="92"/>
+      <c r="G8" s="124"/>
       <c r="H8" s="22"/>
       <c r="I8" s="22"/>
     </row>
@@ -3084,11 +3084,11 @@
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="96" t="s">
+      <c r="F9" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
       <c r="I9" s="16"/>
     </row>
     <row r="10" spans="2:10" ht="16.5" thickBot="1">
@@ -3105,37 +3105,37 @@
     </row>
     <row r="11" spans="2:10" ht="16.5" thickTop="1" thickBot="1"/>
     <row r="12" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B12" s="73" t="s">
+      <c r="B12" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="74"/>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="75"/>
+      <c r="C12" s="106"/>
+      <c r="D12" s="106"/>
+      <c r="E12" s="106"/>
+      <c r="F12" s="107"/>
     </row>
     <row r="13" spans="2:10" ht="15.75" thickBot="1">
-      <c r="B13" s="76"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="78"/>
+      <c r="B13" s="108"/>
+      <c r="C13" s="109"/>
+      <c r="D13" s="109"/>
+      <c r="E13" s="109"/>
+      <c r="F13" s="110"/>
       <c r="J13" s="26"/>
     </row>
     <row r="14" spans="2:10" ht="16.899999999999999" customHeight="1">
-      <c r="B14" s="79" t="s">
+      <c r="B14" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="80"/>
-      <c r="D14" s="80"/>
-      <c r="E14" s="80"/>
-      <c r="F14" s="81"/>
+      <c r="C14" s="112"/>
+      <c r="D14" s="112"/>
+      <c r="E14" s="112"/>
+      <c r="F14" s="113"/>
     </row>
     <row r="15" spans="2:10" ht="16.899999999999999" customHeight="1" thickBot="1">
-      <c r="B15" s="82"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="84"/>
+      <c r="B15" s="114"/>
+      <c r="C15" s="115"/>
+      <c r="D15" s="115"/>
+      <c r="E15" s="115"/>
+      <c r="F15" s="116"/>
     </row>
     <row r="16" spans="2:10">
       <c r="B16" s="27" t="s">
@@ -3150,37 +3150,37 @@
       <c r="E16" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="F16" s="69" t="s">
+      <c r="F16" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="69" t="s">
+      <c r="G16" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="H16" s="67" t="s">
+      <c r="H16" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="109"/>
+      <c r="I16" s="85"/>
     </row>
     <row r="17" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B17" s="159"/>
-      <c r="C17" s="160"/>
-      <c r="D17" s="160"/>
-      <c r="E17" s="160"/>
-      <c r="F17" s="70"/>
-      <c r="G17" s="70"/>
-      <c r="H17" s="68"/>
-      <c r="I17" s="109"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="102"/>
+      <c r="G17" s="102"/>
+      <c r="H17" s="100"/>
+      <c r="I17" s="85"/>
     </row>
     <row r="18" spans="2:11" ht="14.45" customHeight="1">
-      <c r="B18" s="100" t="str">
+      <c r="B18" s="76" t="str">
         <f ca="1">IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the monthly payments to pay back a loan of $"&amp;Random!H19&amp;" in "&amp;Random!H20&amp;" years an APR of "&amp;Random!H21&amp;"% compounded monthly. Find the total amount payed on the loan and the interest payed.")</f>
         <v>Compute the monthly payments to pay back a loan of $2200 in 5 years an APR of 20.29% compounded monthly. Find the total amount payed on the loan and the interest payed.</v>
       </c>
-      <c r="C18" s="101"/>
-      <c r="D18" s="101"/>
-      <c r="E18" s="102"/>
-      <c r="F18" s="97"/>
-      <c r="G18" s="110" t="s">
+      <c r="C18" s="77"/>
+      <c r="D18" s="77"/>
+      <c r="E18" s="78"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="90" t="s">
         <v>97</v>
       </c>
       <c r="H18" s="29" t="s">
@@ -3195,59 +3195,49 @@
       <c r="K18" s="26"/>
     </row>
     <row r="19" spans="2:11">
-      <c r="B19" s="103"/>
-      <c r="C19" s="104"/>
-      <c r="D19" s="104"/>
-      <c r="E19" s="105"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="161"/>
-      <c r="I19" s="162"/>
-      <c r="J19" s="163"/>
+      <c r="B19" s="79"/>
+      <c r="C19" s="80"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="91"/>
+      <c r="H19" s="86"/>
+      <c r="I19" s="88"/>
+      <c r="J19" s="74"/>
       <c r="K19" s="26"/>
     </row>
     <row r="20" spans="2:11" ht="24" customHeight="1" thickBot="1">
-      <c r="B20" s="106"/>
-      <c r="C20" s="107"/>
-      <c r="D20" s="107"/>
-      <c r="E20" s="108"/>
-      <c r="F20" s="99"/>
-      <c r="G20" s="112"/>
-      <c r="H20" s="164"/>
-      <c r="I20" s="165"/>
-      <c r="J20" s="166"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="84"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="92"/>
+      <c r="H20" s="87"/>
+      <c r="I20" s="89"/>
+      <c r="J20" s="75"/>
       <c r="K20" s="26"/>
     </row>
     <row r="21" spans="2:11" ht="15.75" thickBot="1">
       <c r="B21" s="32"/>
-      <c r="F21" s="113" t="s">
+      <c r="F21" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="G21" s="114"/>
-      <c r="H21" s="93" t="s">
+      <c r="G21" s="94"/>
+      <c r="H21" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="I21" s="94"/>
-      <c r="J21" s="95"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="69"/>
       <c r="K21" s="26"/>
     </row>
     <row r="22" spans="2:11" ht="15.75" thickBot="1">
-      <c r="F22" s="115"/>
-      <c r="G22" s="116"/>
+      <c r="F22" s="95"/>
+      <c r="G22" s="96"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="04EZ75vEYzLuSc635yspVl1Pqdtqngx1OL36DW2Rvm2Pv8R8UFoFl8551fCW7aF82cNDLiYmkbGSxpHOls1U0w==" saltValue="Rqqa4jYiaDvVwlJBzKlTNQ==" spinCount="100000" sheet="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="vyuEoK5DDEffeWwxDJKTxx9FX3HNjHl9Y7LdKZgG8ttx81fni5YNsxiQW6hWyzSkAT3Vx1pBl6QBVPR0w8rdsA==" saltValue="+eYfNNLI/Y1Y4nkr6vgXfA==" spinCount="100000" sheet="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="21">
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="B18:E20"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="F21:G22"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="H16:H17"/>
     <mergeCell ref="F16:F17"/>
@@ -3259,6 +3249,16 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="B18:E20"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="F21:G22"/>
   </mergeCells>
   <conditionalFormatting sqref="H19:J19 I20:J20">
     <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
@@ -5474,10 +5474,10 @@
       <c r="G16" s="144" t="s">
         <v>27</v>
       </c>
-      <c r="H16" s="124" t="s">
+      <c r="H16" s="153" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="126"/>
+      <c r="I16" s="155"/>
     </row>
     <row r="17" spans="2:10">
       <c r="B17" s="46">
@@ -5497,18 +5497,18 @@
       </c>
       <c r="F17" s="145"/>
       <c r="G17" s="145"/>
-      <c r="H17" s="125"/>
-      <c r="I17" s="126"/>
+      <c r="H17" s="154"/>
+      <c r="I17" s="155"/>
     </row>
     <row r="18" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B18" s="117" t="s">
+      <c r="B18" s="146" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="118"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="119"/>
-      <c r="F18" s="123"/>
-      <c r="G18" s="146" t="s">
+      <c r="C18" s="147"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="148"/>
+      <c r="F18" s="152"/>
+      <c r="G18" s="128" t="s">
         <v>82</v>
       </c>
       <c r="H18" s="49" t="s">
@@ -5520,12 +5520,12 @@
       <c r="J18" s="51"/>
     </row>
     <row r="19" spans="2:10">
-      <c r="B19" s="117"/>
-      <c r="C19" s="118"/>
-      <c r="D19" s="118"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="123"/>
-      <c r="G19" s="146"/>
+      <c r="B19" s="146"/>
+      <c r="C19" s="147"/>
+      <c r="D19" s="147"/>
+      <c r="E19" s="148"/>
+      <c r="F19" s="152"/>
+      <c r="G19" s="128"/>
       <c r="H19" s="52" t="e">
         <f>Loans!B17*(1+Loans!C17/Loans!D17)^(Loans!D17*Loans!E17)</f>
         <v>#DIV/0!</v>
@@ -5537,12 +5537,12 @@
       <c r="J19" s="51"/>
     </row>
     <row r="20" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B20" s="117"/>
-      <c r="C20" s="118"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="119"/>
-      <c r="F20" s="123"/>
-      <c r="G20" s="146" t="s">
+      <c r="B20" s="146"/>
+      <c r="C20" s="147"/>
+      <c r="D20" s="147"/>
+      <c r="E20" s="148"/>
+      <c r="F20" s="152"/>
+      <c r="G20" s="128" t="s">
         <v>85</v>
       </c>
       <c r="H20" s="54" t="s">
@@ -5556,43 +5556,43 @@
       </c>
     </row>
     <row r="21" spans="2:10">
-      <c r="B21" s="117"/>
-      <c r="C21" s="118"/>
-      <c r="D21" s="118"/>
-      <c r="E21" s="119"/>
-      <c r="F21" s="123"/>
-      <c r="G21" s="146"/>
-      <c r="H21" s="127" t="e">
+      <c r="B21" s="146"/>
+      <c r="C21" s="147"/>
+      <c r="D21" s="147"/>
+      <c r="E21" s="148"/>
+      <c r="F21" s="152"/>
+      <c r="G21" s="128"/>
+      <c r="H21" s="156" t="e">
         <f>Loans!B17*((1+Loans!C17/Loans!D17)^(Loans!D17*Loans!E17)-1)/(Loans!C17/Loans!D17)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I21" s="128">
+      <c r="I21" s="126">
         <f>Loans!B17*Loans!D17*Loans!E17</f>
         <v>0</v>
       </c>
-      <c r="J21" s="128" t="e">
+      <c r="J21" s="126" t="e">
         <f>H21-I21</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="22" spans="2:10">
-      <c r="B22" s="117"/>
-      <c r="C22" s="118"/>
-      <c r="D22" s="118"/>
-      <c r="E22" s="119"/>
-      <c r="F22" s="123"/>
-      <c r="G22" s="146"/>
-      <c r="H22" s="127"/>
-      <c r="I22" s="129"/>
-      <c r="J22" s="129"/>
+      <c r="B22" s="146"/>
+      <c r="C22" s="147"/>
+      <c r="D22" s="147"/>
+      <c r="E22" s="148"/>
+      <c r="F22" s="152"/>
+      <c r="G22" s="128"/>
+      <c r="H22" s="156"/>
+      <c r="I22" s="127"/>
+      <c r="J22" s="127"/>
     </row>
     <row r="23" spans="2:10">
-      <c r="B23" s="117"/>
-      <c r="C23" s="118"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="119"/>
-      <c r="F23" s="123"/>
-      <c r="G23" s="146" t="s">
+      <c r="B23" s="146"/>
+      <c r="C23" s="147"/>
+      <c r="D23" s="147"/>
+      <c r="E23" s="148"/>
+      <c r="F23" s="152"/>
+      <c r="G23" s="128" t="s">
         <v>87</v>
       </c>
       <c r="H23" s="49" t="s">
@@ -5606,35 +5606,35 @@
       </c>
     </row>
     <row r="24" spans="2:10">
-      <c r="B24" s="117"/>
-      <c r="C24" s="118"/>
-      <c r="D24" s="118"/>
-      <c r="E24" s="119"/>
-      <c r="F24" s="123"/>
-      <c r="G24" s="146"/>
-      <c r="H24" s="127" t="e">
+      <c r="B24" s="146"/>
+      <c r="C24" s="147"/>
+      <c r="D24" s="147"/>
+      <c r="E24" s="148"/>
+      <c r="F24" s="152"/>
+      <c r="G24" s="128"/>
+      <c r="H24" s="156" t="e">
         <f>Loans!B17*(Loans!C17/Loans!D17)/(1-(1+Loans!C17/Loans!D17)^(-Loans!D17*Loans!E17))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I24" s="128">
+      <c r="I24" s="126">
         <f>Loans!D17*Loans!E17*Loans!H19</f>
         <v>0</v>
       </c>
-      <c r="J24" s="148">
+      <c r="J24" s="125">
         <f>I24-Loans!B17</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:10" ht="17.45" customHeight="1" thickBot="1">
-      <c r="B25" s="120"/>
-      <c r="C25" s="121"/>
-      <c r="D25" s="121"/>
-      <c r="E25" s="122"/>
-      <c r="F25" s="147"/>
-      <c r="G25" s="149"/>
-      <c r="H25" s="127"/>
-      <c r="I25" s="129"/>
-      <c r="J25" s="148"/>
+      <c r="B25" s="149"/>
+      <c r="C25" s="150"/>
+      <c r="D25" s="150"/>
+      <c r="E25" s="151"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="129"/>
+      <c r="H25" s="156"/>
+      <c r="I25" s="127"/>
+      <c r="J25" s="125"/>
     </row>
     <row r="26" spans="2:10">
       <c r="B26" s="55"/>
@@ -5651,6 +5651,10 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="K6FLfj/2GW8ZCTHv8p2xOh6RoXSFAt/EbNff2TRYiVEiR5k81I441LUk2VqjGrBYfbxIzcyIabf7eIRPuVbGfw==" saltValue="gn8DjQ/CYqWIJUrkECcB7A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="20">
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="F20:F22"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="F23:F25"/>
     <mergeCell ref="J24:J25"/>
     <mergeCell ref="J21:J22"/>
     <mergeCell ref="G23:G25"/>
@@ -5667,10 +5671,6 @@
     <mergeCell ref="I21:I22"/>
     <mergeCell ref="H24:H25"/>
     <mergeCell ref="I24:I25"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="F20:F22"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="F23:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="H18:H21">
     <cfRule type="expression" dxfId="1" priority="2">
@@ -5697,34 +5697,34 @@
   <sheetData>
     <row r="1" spans="2:6" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:6">
-      <c r="B2" s="150" t="s">
+      <c r="B2" s="158" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="151"/>
-      <c r="D2" s="151"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="152"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="160"/>
     </row>
     <row r="3" spans="2:6">
-      <c r="B3" s="153"/>
-      <c r="C3" s="154"/>
-      <c r="D3" s="154"/>
-      <c r="E3" s="154"/>
-      <c r="F3" s="155"/>
+      <c r="B3" s="161"/>
+      <c r="C3" s="162"/>
+      <c r="D3" s="162"/>
+      <c r="E3" s="162"/>
+      <c r="F3" s="163"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="153"/>
-      <c r="C4" s="154"/>
-      <c r="D4" s="154"/>
-      <c r="E4" s="154"/>
-      <c r="F4" s="155"/>
+      <c r="B4" s="161"/>
+      <c r="C4" s="162"/>
+      <c r="D4" s="162"/>
+      <c r="E4" s="162"/>
+      <c r="F4" s="163"/>
     </row>
     <row r="5" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B5" s="156"/>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="157"/>
-      <c r="F5" s="158"/>
+      <c r="B5" s="164"/>
+      <c r="C5" s="165"/>
+      <c r="D5" s="165"/>
+      <c r="E5" s="165"/>
+      <c r="F5" s="166"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5735,15 +5735,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="674b7a4e239a9748c7aaa97e309327a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="600253478e594d1349e02792803dc53a" ns2:_="" ns3:_="">
     <xsd:import namespace="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
@@ -5960,6 +5951,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5971,15 +5971,30 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8D40D51-EB3D-4F2E-911E-703AF067E6CE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
+    <ds:schemaRef ds:uri="18557d39-01b8-4d71-9479-3fad465290ae"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC22AC1B-1134-480D-984D-E3FB18425132}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8D40D51-EB3D-4F2E-911E-703AF067E6CE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
